--- a/jewel pcb/PickAndPlace.xlsx
+++ b/jewel pcb/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB2_2025-11-15" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB2_2025-11-16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="117">
   <si>
     <t>Designator</t>
   </si>
@@ -295,49 +295,73 @@
     <t>-44.118mm</t>
   </si>
   <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>26.155mm</t>
+  </si>
+  <si>
+    <t>-55.148mm</t>
+  </si>
+  <si>
+    <t>CH1</t>
+  </si>
+  <si>
+    <t>31.473mm</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>36.537mm</t>
+  </si>
+  <si>
+    <t>5VB</t>
+  </si>
+  <si>
+    <t>25.266mm</t>
+  </si>
+  <si>
+    <t>-38.257mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>CH7B</t>
+  </si>
+  <si>
+    <t>GNDB</t>
+  </si>
+  <si>
+    <t>37.045mm</t>
+  </si>
+  <si>
     <t>CH7</t>
   </si>
   <si>
-    <t>ZX-SH1.0-3PLT</t>
-  </si>
-  <si>
-    <t>CONN-SMD_3P-P1.00_HDGC_HDGC1002WV-S-3P</t>
+    <t>HC-1.0-3PLT</t>
+  </si>
+  <si>
+    <t>CONN-SMD_3P-P1.00_HC-1.0-3PLT</t>
   </si>
   <si>
     <t>31.369mm</t>
   </si>
   <si>
-    <t>-49.149mm</t>
+    <t>-49.022mm</t>
   </si>
   <si>
     <t>30.369mm</t>
   </si>
   <si>
-    <t>-47.649mm</t>
-  </si>
-  <si>
-    <t>5V</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>26.155mm</t>
-  </si>
-  <si>
-    <t>-55.148mm</t>
-  </si>
-  <si>
-    <t>31.473mm</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>36.537mm</t>
+    <t>-47.622mm</t>
   </si>
 </sst>
 </file>
@@ -714,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -1579,13 +1603,13 @@
         <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K20" t="s">
         <v>22</v>
@@ -1602,31 +1626,31 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1641,36 +1665,36 @@
         <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1685,33 +1709,33 @@
         <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
         <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s">
         <v>105</v>
@@ -1720,16 +1744,148 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="L23">
+        <v>180</v>
+      </c>
+      <c r="M23" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24">
+        <v>180</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25">
+        <v>180</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26">
         <v>0</v>
       </c>
-      <c r="M23" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" t="s">
-        <v>102</v>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
